--- a/Otros Documentos/Matriz de trazabilidad_ Planify.xlsx
+++ b/Otros Documentos/Matriz de trazabilidad_ Planify.xlsx
@@ -295,7 +295,7 @@
     </r>
   </si>
   <si>
-    <t>(Pendiente)</t>
+    <t>-</t>
   </si>
   <si>
     <t>CD-INT-03</t>
